--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,32 +799,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119653870</v>
+        <v>137043418</v>
       </c>
       <c r="B3" t="n">
-        <v>58114</v>
+        <v>58005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,20 +836,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 26992, Kammarbogöl, Sm</t>
+          <t>A 27727, Stormandebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579770</v>
+        <v>579713</v>
       </c>
       <c r="R3" t="n">
-        <v>6398150</v>
+        <v>6398100</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,12 +876,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,13 +901,355 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137043418</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119653870</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 26992, Kammarbogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579770</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398150</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/119653870</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137043414</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 27727, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>579713</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137043414</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137043291</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 27727, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579713</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398100</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137043291</t>
         </is>
       </c>
     </row>
@@ -915,6 +1257,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson</t>
+          <t>Magnus Kasselstrand, Christer Johansson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119653895</v>
+        <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 26992, Kammarbogöl, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579810</v>
+        <v>579557</v>
       </c>
       <c r="R2" t="n">
-        <v>6398204</v>
+        <v>6398116</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,77 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119653895</t>
+          <t>https://artportalen.se/Sighting/137073531</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137043418</v>
+        <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>92917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579713</v>
+        <v>579567</v>
       </c>
       <c r="R3" t="n">
-        <v>6398100</v>
+        <v>6398104</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +860,19 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,77 +887,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137043418</t>
+          <t>https://artportalen.se/Sighting/137074986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119653870</v>
+        <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>92331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>3008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 26992, Kammarbogöl, Sm</t>
+          <t>Ankarsrum tallriterevir, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579770</v>
+        <v>579399</v>
       </c>
       <c r="R4" t="n">
-        <v>6398150</v>
+        <v>6398058</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,12 +969,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Liggande tallåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +1004,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119653870</t>
+          <t>https://artportalen.se/Sighting/137073517</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137043414</v>
+        <v>119653895</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,14 +1064,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 27727, Stormandebo, Sm</t>
+          <t>A 26992, Kammarbogöl, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579713</v>
+        <v>579810</v>
       </c>
       <c r="R5" t="n">
-        <v>6398100</v>
+        <v>6398204</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,12 +1098,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,22 +1128,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson, Gabriel Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137043414</t>
+          <t>https://artportalen.se/Sighting/119653895</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137043291</v>
+        <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,16 +1151,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1171,14 +1170,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1249,7 +1248,1275 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137043418</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137073534</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579726</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398135</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073534</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137074983</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579712</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6398113</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074983</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137073536</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58283</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579588</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6398099</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073536</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119653870</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 26992, Kammarbogöl, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579770</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6398150</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119653870</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137043414</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 27727, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579713</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6398100</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Christer Johansson, Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137043414</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137073535</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579696</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6398111</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073535</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137074982</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579712</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6398113</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074982</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137043291</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 27727, Stormandebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579713</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6398100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137043291</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137073533</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579713</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6398120</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073533</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137074985</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579712</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6398113</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074985</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137073519</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58629</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ankarsrum tallriterevir, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579414</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6398049</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137073519</t>
         </is>
       </c>
     </row>
@@ -1260,6 +2527,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92917</v>
+        <v>92918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92918</v>
+        <v>92924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92924</v>
+        <v>92928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson</t>
+          <t>Christer Johansson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92928</v>
+        <v>92930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson, Gabriel Johansson</t>
+          <t>Christer Johansson, Magnus Kasselstrand, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92930</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Christer Johansson, Magnus Kasselstrand, Gabriel Johansson</t>
+          <t>Magnus Kasselstrand, Christer Johansson, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christer Johansson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2185,7 +2185,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92943</v>
+        <v>92945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -1175,11 +1175,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1399,11 +1395,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ankarsrum, Sm</t>
@@ -1748,11 +1740,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1858,11 +1846,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1980,11 +1964,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ankarsrum, Sm</t>
@@ -2103,11 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92945</v>
+        <v>92948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92948</v>
+        <v>92958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58644</v>
+        <v>58654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92958</v>
+        <v>92959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Christer Johansson</t>
+          <t>Christer Johansson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92959</v>
+        <v>92962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christer Johansson, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Christer Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2161,7 +2161,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58654</v>
+        <v>58656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92962</v>
+        <v>92964</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92964</v>
+        <v>92969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58656</v>
+        <v>58658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92969</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137073531</v>
       </c>
       <c r="B2" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074986</v>
       </c>
       <c r="B3" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137073517</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>137043418</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>137073534</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>137074983</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>137073536</v>
       </c>
       <c r="B9" t="n">
-        <v>58310</v>
+        <v>58313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>137043414</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137073535</v>
       </c>
       <c r="B12" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>137074982</v>
       </c>
       <c r="B13" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>137043291</v>
       </c>
       <c r="B14" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137073533</v>
       </c>
       <c r="B15" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137074985</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>137073519</v>
       </c>
       <c r="B17" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
